--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487034_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487034_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1582</v>
+        <v>4.1881</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9683</v>
+        <v>5.2659</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8101</v>
+        <v>-1.0778</v>
       </c>
       <c r="G2" t="n">
         <v>6.0938</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3393</v>
+        <v>1.3692</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3413</v>
+        <v>0.6389</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9981</v>
+        <v>0.7304</v>
       </c>
       <c r="V2" t="n">
         <v>-4.626</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.56</v>
+        <v>2.8788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0798</v>
+        <v>-0.521</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4801</v>
+        <v>3.3998</v>
       </c>
       <c r="G3" t="n">
         <v>1.9255</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>0.392</v>
+        <v>-0.2892</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6214</v>
+        <v>0.0205</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2294</v>
+        <v>-0.3097</v>
       </c>
       <c r="V3" t="n">
         <v>0.08450000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1751</v>
+        <v>2.3149</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6686</v>
+        <v>-1.3682</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8436</v>
+        <v>3.683</v>
       </c>
       <c r="G4" t="n">
         <v>0.4505</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5618</v>
+        <v>0.7016</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2102</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.772</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>2.1278</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.696</v>
+        <v>2.0431</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5565</v>
+        <v>-0.156</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2526</v>
+        <v>2.199</v>
       </c>
       <c r="G5" t="n">
         <v>0.7958</v>
@@ -844,13 +844,13 @@
         <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0648</v>
+        <v>0.2822</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5208</v>
+        <v>-0.1203</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4561</v>
+        <v>0.4025</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.713</v>
+        <v>1.011</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6706</v>
+        <v>-2.2262</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3836</v>
+        <v>3.2372</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4077</v>
+        <v>-0.0868</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2959</v>
+        <v>2.4323</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1117</v>
+        <v>-2.519</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2462</v>
+        <v>-1.2283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3362</v>
+        <v>2.0854</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-3.3137</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1614</v>
+        <v>1.1416</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0403</v>
+        <v>0.3469</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2017</v>
+        <v>0.7947</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3087</v>
+        <v>-0.1302</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0132</v>
+        <v>-0.2958</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3219</v>
+        <v>0.1656</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5531</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5962</v>
+        <v>-1.7707</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1493</v>
+        <v>2.4103</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9272</v>
+        <v>1.4077</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3385</v>
+        <v>0.2959</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5887</v>
+        <v>1.1117</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3652</v>
+        <v>0.2462</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1554</v>
+        <v>0.3362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5205</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>1.562</v>
+        <v>1.1614</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4938</v>
+        <v>-0.0403</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0682</v>
+        <v>1.2017</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0881</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7297</v>
+        <v>-0.3821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6359</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.2952</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9843</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1226</v>
+        <v>0.4133</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9272</v>
+        <v>-2.8966</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0498</v>
+        <v>3.3099</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0868</v>
+        <v>1.9272</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4323</v>
+        <v>0.3385</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.519</v>
+        <v>1.5887</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2283</v>
+        <v>0.3652</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0854</v>
+        <v>-0.1554</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.3137</v>
+        <v>0.5205</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1416</v>
+        <v>1.562</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3469</v>
+        <v>0.4938</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7947</v>
+        <v>1.0682</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0186</v>
+        <v>0.5899</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9967</v>
+        <v>0.3355</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0218</v>
+        <v>0.2545</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>0.9843</v>
       </c>
       <c r="W8" t="n">
         <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1897</v>
+        <v>0.1521</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6895</v>
+        <v>-1.4204</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4998</v>
+        <v>1.5725</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.07140000000000001</v>
+        <v>1.9711</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.472</v>
+        <v>1.2793</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4006</v>
+        <v>0.6919</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2731</v>
+        <v>0.7228</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2731</v>
+        <v>0.6985</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0243</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2017</v>
+        <v>1.2483</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8011</v>
+        <v>0.5807</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4006</v>
+        <v>0.6676</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.772</v>
+        <v>-1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6536999999999999</v>
+        <v>-0.3751</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5486</v>
+        <v>-0.2131</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1051</v>
+        <v>-0.162</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6163</v>
+        <v>-0.5239</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9211</v>
+        <v>-1.8898</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3048</v>
+        <v>1.3659</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9711</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2793</v>
+        <v>-0.472</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6919</v>
+        <v>0.4006</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7228</v>
+        <v>-1.2731</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6985</v>
+        <v>-1.2731</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2483</v>
+        <v>1.2017</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5807</v>
+        <v>0.8011</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6676</v>
+        <v>0.4006</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1435</v>
+        <v>0.3196</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7139</v>
+        <v>0.3483</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4297</v>
+        <v>-0.0288</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1996</v>
+        <v>-1.0331</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1345</v>
+        <v>-2.8341</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9349</v>
+        <v>1.801</v>
       </c>
       <c r="G11" t="n">
         <v>0.8184</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.0786</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3569</v>
+        <v>-0.0565</v>
       </c>
       <c r="U11" t="n">
-        <v>0.269</v>
+        <v>0.1352</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9488</v>
+        <v>-1.3877</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3664</v>
+        <v>0.0341</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5824</v>
+        <v>-1.4218</v>
       </c>
       <c r="G12" t="n">
         <v>0.8977000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.158</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9769</v>
+        <v>-0.4158</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5605</v>
+        <v>-0.3999</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.489</v>
+        <v>-2.1618</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6586</v>
+        <v>-4.3582</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1696</v>
+        <v>2.1964</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7798</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5162</v>
+        <v>-0.189</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0786</v>
+        <v>0.1054</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.534599999999998</v>
+        <v>8.534400000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.1411</v>
+        <v>-14.1412</v>
       </c>
       <c r="F14" t="n">
-        <v>22.6756</v>
+        <v>22.6754</v>
       </c>
       <c r="G14" t="n">
         <v>14.3497</v>
@@ -1516,28 +1516,28 @@
         <v>14.221</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1286999999999994</v>
+        <v>0.1286999999999989</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8348</v>
+        <v>2.834799999999999</v>
       </c>
       <c r="K14" t="n">
         <v>10.6851</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.850299999999999</v>
+        <v>-7.850300000000001</v>
       </c>
       <c r="M14" t="n">
         <v>11.515</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5357</v>
+        <v>3.535699999999999</v>
       </c>
       <c r="O14" t="n">
         <v>7.979199999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.8601</v>
+        <v>-3.860100000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-22.1958</v>
@@ -1546,10 +1546,10 @@
         <v>18.3358</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5599</v>
+        <v>1.5597</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3506000000000001</v>
+        <v>0.3504999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>1.2094</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1334</v>
+        <v>4.397</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6729</v>
+        <v>2.0707</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4605</v>
+        <v>2.3263</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4543</v>
@@ -1624,13 +1624,13 @@
         <v>3.6672</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9883</v>
+        <v>0.2518</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6869</v>
+        <v>0.0847</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3014</v>
+        <v>0.1672</v>
       </c>
       <c r="V15" t="n">
         <v>4.8274</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1601</v>
+        <v>0.2334</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6117</v>
+        <v>-0.5115</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3125</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1064</v>
+        <v>-0.0331</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0145</v>
+        <v>0.1147</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.121</v>
+        <v>-0.1477</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1394</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5042</v>
+        <v>-1.404</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3647</v>
+        <v>1.338</v>
       </c>
       <c r="G17" t="n">
         <v>0.6055</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2201</v>
+        <v>0.2935</v>
       </c>
       <c r="T17" t="n">
-        <v>0.074</v>
+        <v>0.1742</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1461</v>
+        <v>0.1193</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4401</v>
+        <v>-0.6682</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7404</v>
+        <v>-4.1367</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3003</v>
+        <v>3.4685</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7974</v>
+        <v>-2.1861</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1705</v>
+        <v>-2.3411</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6269</v>
+        <v>0.1549</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.6975</v>
+        <v>-2.1329</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6212</v>
+        <v>-0.8384</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0763</v>
+        <v>-1.2945</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0998</v>
+        <v>-0.0532</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5493</v>
+        <v>-1.5026</v>
       </c>
       <c r="O18" t="n">
         <v>1.4494</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0881</v>
+        <v>3.6672</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6504</v>
+        <v>-0.505</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3385</v>
+        <v>-0.3595</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3119</v>
+        <v>-0.1455</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9859</v>
+        <v>-0.8678</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8793</v>
+        <v>-4.1409</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1066</v>
+        <v>3.2732</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4081</v>
+        <v>-2.7974</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5288</v>
+        <v>-2.1705</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1207</v>
+        <v>-0.6269</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0145</v>
+        <v>-2.6975</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0145</v>
+        <v>-0.6212</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.0763</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3936</v>
+        <v>-0.0998</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5143</v>
+        <v>-1.5493</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1207</v>
+        <v>1.4494</v>
       </c>
       <c r="P19" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>3.0881</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5923</v>
+        <v>0.2228</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8144</v>
+        <v>-0.0621</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2221</v>
+        <v>0.2849</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9421</v>
+        <v>1.5138</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6028</v>
+        <v>-1.3191</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.9378</v>
+        <v>-1.4801</v>
       </c>
       <c r="F20" t="n">
-        <v>3.335</v>
+        <v>0.1611</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1861</v>
+        <v>-1.4081</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3411</v>
+        <v>-1.5288</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1549</v>
+        <v>0.1207</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1329</v>
+        <v>-1.0145</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8384</v>
+        <v>-1.0145</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2945</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0532</v>
+        <v>-0.3936</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5026</v>
+        <v>-0.5143</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4494</v>
+        <v>0.1207</v>
       </c>
       <c r="P20" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.7371</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-1.9301</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.6672</v>
-      </c>
       <c r="S20" t="n">
-        <v>-1.4396</v>
+        <v>0.2591</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1607</v>
+        <v>0.2135</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.279</v>
+        <v>0.0456</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2859</v>
+        <v>-0.9421</v>
       </c>
       <c r="W20" t="n">
         <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3876</v>
+        <v>-1.9978</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3611</v>
+        <v>-0.8964</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9735</v>
+        <v>-1.1014</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1354</v>
+        <v>0.1142</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4239</v>
+        <v>0.8011</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2885</v>
+        <v>-0.6869</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7551</v>
+        <v>0.3674</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4606</v>
+        <v>1.035</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2945</v>
+        <v>-0.6676</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3803</v>
+        <v>-0.2531</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9632</v>
+        <v>-0.2338</v>
       </c>
       <c r="O21" t="n">
-        <v>1.583</v>
+        <v>-0.0193</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7021</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3451</v>
+        <v>-0.3123</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9967</v>
+        <v>-0.2987</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6516999999999999</v>
+        <v>-0.0136</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2859</v>
+        <v>-1.7997</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5322</v>
+        <v>-2.2422</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.297</v>
+        <v>-4.7603</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2352</v>
+        <v>2.5181</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1142</v>
+        <v>-2.1354</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8011</v>
+        <v>-2.4239</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6869</v>
+        <v>0.2885</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3674</v>
+        <v>-1.7551</v>
       </c>
       <c r="K22" t="n">
-        <v>1.035</v>
+        <v>-0.4606</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6676</v>
+        <v>-1.2945</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2531</v>
+        <v>-0.3803</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2338</v>
+        <v>-1.9632</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0193</v>
+        <v>1.583</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R22" t="n">
-        <v>0.965</v>
+        <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8467</v>
+        <v>-0.1996</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6993</v>
+        <v>-0.3959</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1474</v>
+        <v>0.1963</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>0.2859</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2826</v>
+        <v>-2.4408</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5896</v>
+        <v>-4.9888</v>
       </c>
       <c r="F23" t="n">
-        <v>2.307</v>
+        <v>2.548</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3664</v>
@@ -2248,13 +2248,13 @@
         <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9089</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6993</v>
+        <v>-0.0985</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2095</v>
+        <v>0.0314</v>
       </c>
       <c r="V23" t="n">
         <v>0.5717</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4573</v>
+        <v>-2.8955</v>
       </c>
       <c r="E24" t="n">
         <v>-2.4274</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0298</v>
+        <v>-0.468</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4091</v>
@@ -2326,13 +2326,13 @@
         <v>2.5091</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3643</v>
+        <v>-0.8024</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5816</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7826</v>
+        <v>-0.2208</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.534400000000002</v>
+        <v>-7.867100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-22.6756</v>
+        <v>-22.6754</v>
       </c>
       <c r="F25" t="n">
-        <v>14.1411</v>
+        <v>14.8088</v>
       </c>
       <c r="G25" t="n">
         <v>-14.3496</v>
@@ -2374,7 +2374,7 @@
         <v>-14.2212</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1284999999999999</v>
+        <v>-0.1284999999999997</v>
       </c>
       <c r="J25" t="n">
         <v>-11.5148</v>
@@ -2404,13 +2404,13 @@
         <v>22.1959</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5599</v>
+        <v>-0.8923</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2093</v>
+        <v>-1.2092</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3504999999999999</v>
+        <v>0.3170999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>3.5149</v>
